--- a/画面項目仕様書.xlsx
+++ b/画面項目仕様書.xlsx
@@ -2081,7 +2081,7 @@
       <c r="G56" s="2" t="inlineStr"/>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Google Books API から取得した書籍情報を下の入力欄に自動入力（画面遷移なし）。検索中は「検索中...」と表示</t>
+          <t>Google Books API から取得した書籍情報を下の入力欄に自動入力（画面遷移なし）。検索中は「検索中...」と表示。取得に失敗した場合はエラーメッセージを表示し、入力欄は変更しない</t>
         </is>
       </c>
     </row>
